--- a/tams-valuation-parent/tams-valuation-lossmodel/src/main/resources/tpl/Specialassets001.xlsx
+++ b/tams-valuation-parent/tams-valuation-lossmodel/src/main/resources/tpl/Specialassets001.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="135" windowWidth="14805" windowHeight="7980"/>
+    <workbookView xWindow="240" yWindow="132" windowWidth="14808" windowHeight="7980"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,18 +16,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>评级类型</t>
-  </si>
-  <si>
-    <t>评级机构</t>
   </si>
   <si>
     <t>资产名称</t>
   </si>
   <si>
     <t>资产代码</t>
+  </si>
+  <si>
+    <t>评级机构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定评级机构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -96,12 +101,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -143,7 +151,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -178,7 +186,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -387,26 +395,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="34.875" customWidth="1"/>
-    <col min="2" max="2" width="37.875" customWidth="1"/>
-    <col min="3" max="3" width="41.5" customWidth="1"/>
-    <col min="4" max="4" width="23.875" customWidth="1"/>
+    <col min="1" max="1" width="34.88671875" customWidth="1"/>
+    <col min="2" max="3" width="37.88671875" customWidth="1"/>
+    <col min="4" max="4" width="41.44140625" customWidth="1"/>
+    <col min="5" max="5" width="23.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="13.5" customHeight="1">
       <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>2</v>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
@@ -420,7 +431,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -430,7 +441,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
